--- a/data/trans_camb/P12_3_R-Clase-trans_camb.xlsx
+++ b/data/trans_camb/P12_3_R-Clase-trans_camb.xlsx
@@ -677,47 +677,47 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-2,5; 3,78</t>
+          <t>-2,52; 3,96</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-2,71; 3,52</t>
+          <t>-2,52; 3,45</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>0,9; 7,57</t>
+          <t>0,78; 7,19</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-2,92; 5,39</t>
+          <t>-3,38; 5,27</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-5,64; 0,93</t>
+          <t>-5,87; 1,22</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-1,0; 5,8</t>
+          <t>-1,17; 5,75</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>-1,47; 3,49</t>
+          <t>-1,73; 3,38</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>-2,88; 1,5</t>
+          <t>-2,78; 1,69</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>1,03; 5,66</t>
+          <t>1,06; 5,83</t>
         </is>
       </c>
     </row>
@@ -783,47 +783,47 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-41,78; 128,28</t>
+          <t>-41,27; 112,65</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-46,2; 109,53</t>
+          <t>-41,8; 113,3</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>11,55; 234,63</t>
+          <t>5,41; 202,5</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-41,28; 126,45</t>
+          <t>-44,31; 118,98</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-68,02; 26,63</t>
+          <t>-69,16; 37,97</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>-15,36; 146,23</t>
+          <t>-14,41; 141,18</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>-25,37; 86,48</t>
+          <t>-27,95; 85,95</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>-44,82; 37,34</t>
+          <t>-44,08; 42,69</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>14,6; 136,37</t>
+          <t>15,32; 144,22</t>
         </is>
       </c>
     </row>
@@ -893,47 +893,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-1,0; 5,91</t>
+          <t>-0,96; 5,97</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-0,66; 6,25</t>
+          <t>-0,74; 6,13</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>1,91; 9,57</t>
+          <t>1,98; 9,26</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-2,8; 6,53</t>
+          <t>-2,64; 6,64</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-3,23; 5,05</t>
+          <t>-3,54; 5,16</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-3,09; 4,66</t>
+          <t>-2,74; 4,9</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>-0,64; 5,01</t>
+          <t>-0,99; 4,61</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>-0,81; 4,38</t>
+          <t>-0,63; 4,29</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>0,89; 5,91</t>
+          <t>0,78; 5,96</t>
         </is>
       </c>
     </row>
@@ -999,47 +999,47 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-25,11; 262,88</t>
+          <t>-22,22; 285,11</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-16,58; 290,19</t>
+          <t>-18,89; 270,98</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>29,34; 438,64</t>
+          <t>19,37; 422,11</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-29,57; 104,77</t>
+          <t>-26,67; 109,75</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-33,25; 81,93</t>
+          <t>-34,39; 86,69</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-29,64; 77,49</t>
+          <t>-28,79; 82,26</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>-9,97; 112,92</t>
+          <t>-14,2; 95,34</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>-11,59; 95,93</t>
+          <t>-9,99; 87,89</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>11,59; 127,0</t>
+          <t>8,67; 120,5</t>
         </is>
       </c>
     </row>
@@ -1109,47 +1109,47 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>1,01; 6,81</t>
+          <t>1,06; 6,99</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-0,01; 6,32</t>
+          <t>0,06; 6,11</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-3,01; 8,44</t>
+          <t>-4,53; 8,6</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-7,78; 5,82</t>
+          <t>-8,01; 5,53</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-5,72; 9,55</t>
+          <t>-6,01; 9,62</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-3,88; 8,63</t>
+          <t>-4,55; 8,95</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>0,19; 5,86</t>
+          <t>0,25; 5,93</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>-0,13; 5,91</t>
+          <t>-0,25; 5,74</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>-4,22; 7,61</t>
+          <t>-3,72; 7,39</t>
         </is>
       </c>
     </row>
@@ -1215,47 +1215,47 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>10,0; 180,27</t>
+          <t>12,46; 186,24</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>-0,94; 174,35</t>
+          <t>-0,16; 161,88</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>-44,58; 185,36</t>
+          <t>-59,8; 189,39</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>-46,45; 72,83</t>
+          <t>-48,4; 75,0</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>-37,51; 114,1</t>
+          <t>-40,23; 116,44</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>-25,05; 103,59</t>
+          <t>-27,92; 111,29</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>1,55; 109,89</t>
+          <t>1,86; 116,04</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>-1,3; 112,1</t>
+          <t>-3,47; 106,28</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>-49,79; 124,68</t>
+          <t>-46,58; 119,42</t>
         </is>
       </c>
     </row>
@@ -1325,47 +1325,47 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>1,7; 6,11</t>
+          <t>1,64; 6,12</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>0,09; 4,2</t>
+          <t>-0,18; 3,92</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>3,73; 9,4</t>
+          <t>3,56; 9,24</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>1,87; 8,5</t>
+          <t>1,87; 8,49</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>-0,89; 4,88</t>
+          <t>-0,8; 5,2</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>-3,02; 6,29</t>
+          <t>-3,54; 6,21</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>2,63; 6,35</t>
+          <t>2,53; 6,12</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>0,43; 3,86</t>
+          <t>0,5; 3,92</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>0,81; 7,01</t>
+          <t>1,05; 7,05</t>
         </is>
       </c>
     </row>
@@ -1431,47 +1431,47 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>24,77; 121,65</t>
+          <t>21,41; 116,49</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>1,07; 78,19</t>
+          <t>-3,14; 75,71</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>54,58; 176,72</t>
+          <t>49,89; 172,9</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>18,51; 132,99</t>
+          <t>19,98; 133,21</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>-9,34; 72,21</t>
+          <t>-8,81; 81,57</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>-33,53; 86,74</t>
+          <t>-34,01; 88,57</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>35,45; 104,53</t>
+          <t>33,18; 98,34</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>5,59; 65,2</t>
+          <t>6,71; 65,09</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>14,97; 112,58</t>
+          <t>17,67; 114,11</t>
         </is>
       </c>
     </row>
@@ -1541,47 +1541,47 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>-0,18; 6,72</t>
+          <t>-0,11; 6,79</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>1,19; 7,75</t>
+          <t>0,95; 8,03</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>2,2; 9,2</t>
+          <t>1,85; 9,19</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>5,46; 13,04</t>
+          <t>5,33; 12,86</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>5,73; 13,69</t>
+          <t>5,95; 13,5</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>2,36; 11,29</t>
+          <t>2,85; 11,31</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>4,21; 9,73</t>
+          <t>4,06; 9,52</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>4,26; 9,63</t>
+          <t>4,56; 9,82</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>3,81; 9,54</t>
+          <t>4,09; 9,98</t>
         </is>
       </c>
     </row>
@@ -1647,47 +1647,47 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>-3,59; 233,96</t>
+          <t>-4,02; 215,4</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>12,78; 237,24</t>
+          <t>9,44; 243,0</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>25,57; 280,93</t>
+          <t>24,88; 303,27</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>50,7; 190,65</t>
+          <t>48,59; 178,2</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>53,54; 200,27</t>
+          <t>55,18; 187,04</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>25,34; 158,02</t>
+          <t>27,08; 155,6</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>43,45; 155,78</t>
+          <t>44,34; 161,71</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
         <is>
-          <t>48,29; 157,12</t>
+          <t>47,33; 163,14</t>
         </is>
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>45,64; 157,4</t>
+          <t>47,06; 170,1</t>
         </is>
       </c>
     </row>
@@ -1757,47 +1757,47 @@
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
-          <t>-1,41; 5,58</t>
+          <t>-1,39; 5,34</t>
         </is>
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>-3,63; 1,84</t>
+          <t>-3,53; 1,83</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>-1,31; 7,85</t>
+          <t>-1,52; 8,52</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>2,05; 7,29</t>
+          <t>1,86; 7,07</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>0,24; 5,44</t>
+          <t>0,38; 5,67</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>4,82; 10,36</t>
+          <t>4,63; 10,56</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>1,78; 6,32</t>
+          <t>1,84; 6,16</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
         <is>
-          <t>-0,15; 4,16</t>
+          <t>-0,08; 4,07</t>
         </is>
       </c>
       <c r="K25" s="2" t="inlineStr">
         <is>
-          <t>3,61; 8,6</t>
+          <t>3,63; 8,57</t>
         </is>
       </c>
     </row>
@@ -1863,47 +1863,47 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>-32,11; 272,69</t>
+          <t>-34,04; 230,67</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>-75,24; 99,06</t>
+          <t>-76,22; 93,28</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>-31,66; 412,98</t>
+          <t>-37,94; 323,49</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>20,58; 96,6</t>
+          <t>18,38; 91,31</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>2,39; 70,13</t>
+          <t>3,97; 72,69</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>49,93; 136,08</t>
+          <t>45,23; 131,14</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>20,11; 90,64</t>
+          <t>21,2; 89,31</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
         <is>
-          <t>-1,97; 61,72</t>
+          <t>-0,9; 59,9</t>
         </is>
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>39,45; 122,1</t>
+          <t>39,67; 122,16</t>
         </is>
       </c>
     </row>
@@ -1973,47 +1973,47 @@
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
-          <t>1,8; 4,26</t>
+          <t>1,71; 4,28</t>
         </is>
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>1,13; 3,63</t>
+          <t>1,14; 3,55</t>
         </is>
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>2,43; 6,41</t>
+          <t>2,42; 6,4</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>3,15; 6,35</t>
+          <t>3,29; 6,32</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
         <is>
-          <t>1,9; 4,79</t>
+          <t>1,86; 4,92</t>
         </is>
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>2,31; 6,04</t>
+          <t>1,86; 6,21</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>2,98; 4,92</t>
+          <t>2,96; 5,01</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
         <is>
-          <t>1,87; 3,8</t>
+          <t>1,88; 3,71</t>
         </is>
       </c>
       <c r="K29" s="2" t="inlineStr">
         <is>
-          <t>3,03; 5,81</t>
+          <t>2,86; 5,79</t>
         </is>
       </c>
     </row>
@@ -2079,47 +2079,47 @@
       </c>
       <c r="C31" s="2" t="inlineStr">
         <is>
-          <t>30,59; 93,9</t>
+          <t>30,53; 93,8</t>
         </is>
       </c>
       <c r="D31" s="2" t="inlineStr">
         <is>
-          <t>20,08; 79,57</t>
+          <t>20,06; 77,72</t>
         </is>
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>46,47; 141,71</t>
+          <t>47,73; 143,02</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>34,49; 81,59</t>
+          <t>35,78; 81,75</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
         <is>
-          <t>20,04; 60,6</t>
+          <t>20,91; 63,17</t>
         </is>
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>26,73; 77,84</t>
+          <t>22,07; 78,51</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>41,34; 77,0</t>
+          <t>41,32; 79,42</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
         <is>
-          <t>25,71; 59,95</t>
+          <t>26,18; 57,96</t>
         </is>
       </c>
       <c r="K31" s="2" t="inlineStr">
         <is>
-          <t>43,47; 89,54</t>
+          <t>42,85; 90,98</t>
         </is>
       </c>
     </row>

--- a/data/trans_camb/P12_3_R-Clase-trans_camb.xlsx
+++ b/data/trans_camb/P12_3_R-Clase-trans_camb.xlsx
@@ -634,7 +634,7 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>3,94</t>
+          <t>3,75</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
@@ -649,7 +649,7 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>2,59</t>
+          <t>3,1</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
@@ -664,7 +664,7 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>3,41</t>
+          <t>3,55</t>
         </is>
       </c>
     </row>
@@ -677,47 +677,47 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-2,52; 3,96</t>
+          <t>-2,39; 3,77</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-2,52; 3,45</t>
+          <t>-2,53; 3,59</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>0,78; 7,19</t>
+          <t>0,49; 7,2</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-3,38; 5,27</t>
+          <t>-2,64; 5,25</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-5,87; 1,22</t>
+          <t>-5,72; 1,33</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-1,17; 5,75</t>
+          <t>-0,8; 6,03</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>-1,73; 3,38</t>
+          <t>-1,6; 3,27</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>-2,78; 1,69</t>
+          <t>-2,76; 1,72</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>1,06; 5,83</t>
+          <t>1,23; 5,8</t>
         </is>
       </c>
     </row>
@@ -740,7 +740,7 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>84,91%</t>
+          <t>80,96%</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
@@ -755,7 +755,7 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>43,19%</t>
+          <t>51,65%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
@@ -770,7 +770,7 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>65,92%</t>
+          <t>68,66%</t>
         </is>
       </c>
     </row>
@@ -783,47 +783,47 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-41,27; 112,65</t>
+          <t>-41,8; 115,56</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-41,8; 113,3</t>
+          <t>-43,55; 110,62</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>5,41; 202,5</t>
+          <t>2,96; 215,37</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-44,31; 118,98</t>
+          <t>-37,29; 132,31</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-69,16; 37,97</t>
+          <t>-69,41; 37,83</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>-14,41; 141,18</t>
+          <t>-8,8; 151,03</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>-27,95; 85,95</t>
+          <t>-25,23; 85,91</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>-44,08; 42,69</t>
+          <t>-43,3; 47,52</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>15,32; 144,22</t>
+          <t>18,67; 145,22</t>
         </is>
       </c>
     </row>
@@ -850,7 +850,7 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>5,73</t>
+          <t>5,94</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
@@ -865,7 +865,7 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>1,03</t>
+          <t>1,52</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
@@ -880,7 +880,7 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>3,38</t>
+          <t>3,71</t>
         </is>
       </c>
     </row>
@@ -893,47 +893,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-0,96; 5,97</t>
+          <t>-0,89; 5,83</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-0,74; 6,13</t>
+          <t>-0,62; 6,19</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>1,98; 9,26</t>
+          <t>2,92; 9,93</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-2,64; 6,64</t>
+          <t>-2,58; 6,27</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-3,54; 5,16</t>
+          <t>-3,38; 5,09</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-2,74; 4,9</t>
+          <t>-2,28; 5,27</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>-0,99; 4,61</t>
+          <t>-0,68; 5,08</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>-0,63; 4,29</t>
+          <t>-0,75; 4,48</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>0,78; 5,96</t>
+          <t>1,03; 6,01</t>
         </is>
       </c>
     </row>
@@ -956,7 +956,7 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>155,27%</t>
+          <t>161,11%</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
@@ -971,7 +971,7 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>12,73%</t>
+          <t>18,72%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
@@ -986,7 +986,7 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>57,14%</t>
+          <t>62,87%</t>
         </is>
       </c>
     </row>
@@ -999,47 +999,47 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-22,22; 285,11</t>
+          <t>-20,53; 273,03</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-18,89; 270,98</t>
+          <t>-16,87; 286,84</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>19,37; 422,11</t>
+          <t>40,1; 454,9</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-26,67; 109,75</t>
+          <t>-27,5; 103,19</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-34,39; 86,69</t>
+          <t>-33,7; 82,54</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-28,79; 82,26</t>
+          <t>-22,88; 88,21</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>-14,2; 95,34</t>
+          <t>-10,25; 107,4</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>-9,99; 87,89</t>
+          <t>-10,94; 96,04</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>8,67; 120,5</t>
+          <t>12,82; 128,74</t>
         </is>
       </c>
     </row>
@@ -1066,7 +1066,7 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>2,96</t>
+          <t>7,75</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
@@ -1081,7 +1081,7 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>2,89</t>
+          <t>3,04</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
@@ -1096,7 +1096,7 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>2,69</t>
+          <t>6,74</t>
         </is>
       </c>
     </row>
@@ -1109,47 +1109,47 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>1,06; 6,99</t>
+          <t>1,0; 6,96</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>0,06; 6,11</t>
+          <t>0,18; 6,46</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-4,53; 8,6</t>
+          <t>4,32; 11,78</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-8,01; 5,53</t>
+          <t>-7,66; 5,15</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-6,01; 9,62</t>
+          <t>-6,26; 9,03</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-4,55; 8,95</t>
+          <t>-3,28; 10,29</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>0,25; 5,93</t>
+          <t>0,45; 5,86</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>-0,25; 5,74</t>
+          <t>-0,46; 5,75</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>-3,72; 7,39</t>
+          <t>3,88; 10,12</t>
         </is>
       </c>
     </row>
@@ -1172,7 +1172,7 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>58,76%</t>
+          <t>153,96%</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
@@ -1187,7 +1187,7 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>24,12%</t>
+          <t>25,38%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
@@ -1202,7 +1202,7 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>40,33%</t>
+          <t>101,06%</t>
         </is>
       </c>
     </row>
@@ -1215,47 +1215,47 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>12,46; 186,24</t>
+          <t>11,77; 192,39</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>-0,16; 161,88</t>
+          <t>-0,89; 173,14</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>-59,8; 189,39</t>
+          <t>62,45; 315,52</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>-48,4; 75,0</t>
+          <t>-46,87; 64,56</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>-40,23; 116,44</t>
+          <t>-41,88; 108,34</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>-27,92; 111,29</t>
+          <t>-22,49; 136,97</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>1,86; 116,04</t>
+          <t>3,41; 111,0</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>-3,47; 106,28</t>
+          <t>-6,22; 110,79</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>-46,58; 119,42</t>
+          <t>43,51; 184,37</t>
         </is>
       </c>
     </row>
@@ -1282,7 +1282,7 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>6,2</t>
+          <t>5,83</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
@@ -1297,7 +1297,7 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>2,47</t>
+          <t>5,76</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
@@ -1312,7 +1312,7 @@
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>4,6</t>
+          <t>5,92</t>
         </is>
       </c>
     </row>
@@ -1325,47 +1325,47 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>1,64; 6,12</t>
+          <t>1,77; 6,2</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>-0,18; 3,92</t>
+          <t>0,06; 4,16</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>3,56; 9,24</t>
+          <t>3,55; 8,29</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>1,87; 8,49</t>
+          <t>1,88; 8,28</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>-0,8; 5,2</t>
+          <t>-0,93; 4,88</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>-3,54; 6,21</t>
+          <t>2,73; 8,3</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>2,53; 6,12</t>
+          <t>2,38; 6,17</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>0,5; 3,92</t>
+          <t>0,35; 3,69</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>1,05; 7,05</t>
+          <t>4,23; 7,9</t>
         </is>
       </c>
     </row>
@@ -1388,7 +1388,7 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>101,73%</t>
+          <t>95,66%</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
@@ -1403,7 +1403,7 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>31,34%</t>
+          <t>73,03%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
@@ -1418,7 +1418,7 @@
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>68,2%</t>
+          <t>87,68%</t>
         </is>
       </c>
     </row>
@@ -1431,47 +1431,47 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>21,41; 116,49</t>
+          <t>23,1; 119,46</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>-3,14; 75,71</t>
+          <t>0,53; 79,88</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>49,89; 172,9</t>
+          <t>46,02; 155,2</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>19,98; 133,21</t>
+          <t>20,22; 123,68</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>-8,81; 81,57</t>
+          <t>-10,33; 74,63</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>-34,01; 88,57</t>
+          <t>28,7; 124,47</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>33,18; 98,34</t>
+          <t>31,44; 103,48</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>6,71; 65,09</t>
+          <t>4,4; 61,46</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>17,67; 114,11</t>
+          <t>55,48; 132,36</t>
         </is>
       </c>
     </row>
@@ -1498,7 +1498,7 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>5,75</t>
+          <t>5,46</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
@@ -1513,7 +1513,7 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>7,72</t>
+          <t>10,26</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
@@ -1528,7 +1528,7 @@
       </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>7,09</t>
+          <t>8,22</t>
         </is>
       </c>
     </row>
@@ -1541,47 +1541,47 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>-0,11; 6,79</t>
+          <t>0,15; 6,82</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>0,95; 8,03</t>
+          <t>1,17; 8,08</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>1,85; 9,19</t>
+          <t>1,54; 8,7</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>5,33; 12,86</t>
+          <t>5,13; 12,98</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>5,95; 13,5</t>
+          <t>5,81; 13,2</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>2,85; 11,31</t>
+          <t>7,17; 13,36</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>4,06; 9,52</t>
+          <t>4,18; 9,5</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>4,56; 9,82</t>
+          <t>4,67; 9,8</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>4,09; 9,98</t>
+          <t>5,57; 10,55</t>
         </is>
       </c>
     </row>
@@ -1604,7 +1604,7 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>116,27%</t>
+          <t>110,34%</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
@@ -1619,7 +1619,7 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>86,73%</t>
+          <t>115,31%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
@@ -1634,7 +1634,7 @@
       </c>
       <c r="K22" s="2" t="inlineStr">
         <is>
-          <t>95,94%</t>
+          <t>111,17%</t>
         </is>
       </c>
     </row>
@@ -1647,54 +1647,54 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>-4,02; 215,4</t>
+          <t>1,08; 226,34</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>9,44; 243,0</t>
+          <t>10,32; 253,99</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>24,88; 303,27</t>
+          <t>18,92; 275,37</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>48,59; 178,2</t>
+          <t>45,36; 181,31</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>55,18; 187,04</t>
+          <t>52,35; 184,18</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>27,08; 155,6</t>
+          <t>63,93; 189,3</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>44,34; 161,71</t>
+          <t>46,1; 153,18</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
         <is>
-          <t>47,33; 163,14</t>
+          <t>51,8; 164,06</t>
         </is>
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>47,06; 170,1</t>
+          <t>62,8; 175,37</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="1" t="inlineStr">
         <is>
-          <t>6.0</t>
+          <t>No ha trabajado</t>
         </is>
       </c>
       <c r="B24" s="3" t="inlineStr">
@@ -1714,7 +1714,7 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>2,19</t>
+          <t>3,4</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
@@ -1729,7 +1729,7 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>7,49</t>
+          <t>7,55</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
@@ -1744,7 +1744,7 @@
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>5,95</t>
+          <t>6,49</t>
         </is>
       </c>
     </row>
@@ -1757,47 +1757,47 @@
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
-          <t>-1,39; 5,34</t>
+          <t>-1,57; 5,43</t>
         </is>
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>-3,53; 1,83</t>
+          <t>-4,15; 1,54</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>-1,52; 8,52</t>
+          <t>-0,26; 9,39</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>1,86; 7,07</t>
+          <t>1,9; 6,79</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>0,38; 5,67</t>
+          <t>0,37; 5,25</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>4,63; 10,56</t>
+          <t>4,76; 10,21</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>1,84; 6,16</t>
+          <t>1,87; 6,38</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
         <is>
-          <t>-0,08; 4,07</t>
+          <t>-0,08; 4,29</t>
         </is>
       </c>
       <c r="K25" s="2" t="inlineStr">
         <is>
-          <t>3,63; 8,57</t>
+          <t>4,12; 8,91</t>
         </is>
       </c>
     </row>
@@ -1820,7 +1820,7 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>62,51%</t>
+          <t>97,13%</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
@@ -1835,7 +1835,7 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>84,24%</t>
+          <t>84,97%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
@@ -1850,7 +1850,7 @@
       </c>
       <c r="K26" s="2" t="inlineStr">
         <is>
-          <t>75,88%</t>
+          <t>82,74%</t>
         </is>
       </c>
     </row>
@@ -1863,47 +1863,47 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>-34,04; 230,67</t>
+          <t>-33,23; 260,26</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>-76,22; 93,28</t>
+          <t>-75,98; 84,6</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>-37,94; 323,49</t>
+          <t>-16,11; 395,52</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>18,38; 91,31</t>
+          <t>19,19; 88,7</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>3,97; 72,69</t>
+          <t>3,91; 66,91</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>45,23; 131,14</t>
+          <t>45,54; 131,79</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>21,2; 89,31</t>
+          <t>20,14; 90,76</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
         <is>
-          <t>-0,9; 59,9</t>
+          <t>-0,94; 61,15</t>
         </is>
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>39,67; 122,16</t>
+          <t>45,48; 124,73</t>
         </is>
       </c>
     </row>
@@ -1930,7 +1930,7 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>4,73</t>
+          <t>5,48</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
@@ -1945,7 +1945,7 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>4,48</t>
+          <t>6,06</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
@@ -1960,7 +1960,7 @@
       </c>
       <c r="K28" s="2" t="inlineStr">
         <is>
-          <t>4,62</t>
+          <t>5,8</t>
         </is>
       </c>
     </row>
@@ -1973,47 +1973,47 @@
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
-          <t>1,71; 4,28</t>
+          <t>1,78; 4,33</t>
         </is>
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>1,14; 3,55</t>
+          <t>1,12; 3,51</t>
         </is>
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>2,42; 6,4</t>
+          <t>4,1; 6,93</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>3,29; 6,32</t>
+          <t>3,19; 6,31</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
         <is>
-          <t>1,86; 4,92</t>
+          <t>1,85; 4,87</t>
         </is>
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>1,86; 6,21</t>
+          <t>4,73; 7,45</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>2,96; 5,01</t>
+          <t>2,86; 4,91</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
         <is>
-          <t>1,88; 3,71</t>
+          <t>1,8; 3,86</t>
         </is>
       </c>
       <c r="K29" s="2" t="inlineStr">
         <is>
-          <t>2,86; 5,79</t>
+          <t>4,79; 6,77</t>
         </is>
       </c>
     </row>
@@ -2036,7 +2036,7 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>93,08%</t>
+          <t>107,92%</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
@@ -2051,7 +2051,7 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>52,86%</t>
+          <t>71,46%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
@@ -2066,7 +2066,7 @@
       </c>
       <c r="K30" s="2" t="inlineStr">
         <is>
-          <t>67,92%</t>
+          <t>85,16%</t>
         </is>
       </c>
     </row>
@@ -2079,47 +2079,47 @@
       </c>
       <c r="C31" s="2" t="inlineStr">
         <is>
-          <t>30,53; 93,8</t>
+          <t>31,07; 95,06</t>
         </is>
       </c>
       <c r="D31" s="2" t="inlineStr">
         <is>
-          <t>20,06; 77,72</t>
+          <t>19,54; 78,51</t>
         </is>
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>47,73; 143,02</t>
+          <t>72,14; 151,77</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>35,78; 81,75</t>
+          <t>35,01; 81,52</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
         <is>
-          <t>20,91; 63,17</t>
+          <t>20,7; 63,1</t>
         </is>
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>22,07; 78,51</t>
+          <t>50,62; 97,48</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>41,32; 79,42</t>
+          <t>39,91; 79,05</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
         <is>
-          <t>26,18; 57,96</t>
+          <t>24,78; 61,41</t>
         </is>
       </c>
       <c r="K31" s="2" t="inlineStr">
         <is>
-          <t>42,85; 90,98</t>
+          <t>65,65; 105,3</t>
         </is>
       </c>
     </row>
